--- a/data/raw/test_data.xlsx
+++ b/data/raw/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BenPC\projects\Project1_DataScience\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2500F4EB-B885-4389-892F-B4534DDFB7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8326ED-AD5B-464C-8729-DD91E3C214B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{6E01BA4A-0894-44B2-B2DD-D11F5FC8933B}"/>
+    <workbookView xWindow="3948" yWindow="2616" windowWidth="23040" windowHeight="12168" xr2:uid="{6E01BA4A-0894-44B2-B2DD-D11F5FC8933B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1257,6 +1257,12 @@
       <c r="M15" t="s">
         <v>74</v>
       </c>
+      <c r="Q15">
+        <v>34.426678699999997</v>
+      </c>
+      <c r="R15">
+        <v>-119.7111968</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
